--- a/artfynd/A 25319-2026 artfynd.xlsx
+++ b/artfynd/A 25319-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1022,6 +1022,114 @@
       <c r="AZ4" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134401403</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137340316</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58189</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långängen, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>660503</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6557188</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137340316</t>
         </is>
       </c>
     </row>
@@ -1030,6 +1138,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25319-2026 artfynd.xlsx
+++ b/artfynd/A 25319-2026 artfynd.xlsx
@@ -1030,7 +1030,7 @@
         <v>137340316</v>
       </c>
       <c r="B5" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25319-2026 artfynd.xlsx
+++ b/artfynd/A 25319-2026 artfynd.xlsx
@@ -1030,7 +1030,7 @@
         <v>137340316</v>
       </c>
       <c r="B5" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 25319-2026 artfynd.xlsx
+++ b/artfynd/A 25319-2026 artfynd.xlsx
@@ -1030,7 +1030,7 @@
         <v>137340316</v>
       </c>
       <c r="B5" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
